--- a/tooltask/reports/pr_report.xlsx
+++ b/tooltask/reports/pr_report.xlsx
@@ -413,13 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -440,134 +435,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Update list_prs.yml</t>
+          <t>Create list_prs.yml</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
-        <is>
-          <t>Mounashree-2310</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Update list_prs.yml</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Mounashree-2310</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Update list_prs.yml</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Mounashree-2310</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Update list_prs.yml</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Mounashree-2310</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Update list_prs.yml</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Mounashree-2310</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Update list_prs.yml</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Mounashree-2310</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Update list_prs.yml</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Mounashree-2310</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Update README.md</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Mounashree-2310</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Update list_prs.yml</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t>Mounashree-2310</t>
         </is>
